--- a/data/Saxony_sean.xlsx
+++ b/data/Saxony_sean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anitasanchez/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adam\Documents\GitHub\ADDRESS-adit_drainage_solute_source_control\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F411FD6C-649C-414E-9C61-886EC9B5BFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C843E35-F104-444F-99D2-E1C73769DE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16120" xr2:uid="{8C891EF7-7223-A448-A31D-BFA0BA5AE64B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8C891EF7-7223-A448-A31D-BFA0BA5AE64B}"/>
   </bookViews>
   <sheets>
     <sheet name="data_drainages" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -59,9 +57,6 @@
     <t>Temp</t>
   </si>
   <si>
-    <t>EC_𝝁s/cm</t>
-  </si>
-  <si>
     <t>pH</t>
   </si>
   <si>
@@ -195,6 +190,9 @@
   </si>
   <si>
     <t>TRS</t>
+  </si>
+  <si>
+    <t>EC_us/cm</t>
   </si>
 </sst>
 </file>
@@ -206,7 +204,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -217,8 +215,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -253,7 +251,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -586,30 +584,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7081186-7307-4B42-803A-896AB439F30E}">
   <dimension ref="A1:AB30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.84375" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.1640625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="1"/>
-    <col min="7" max="7" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.83203125" style="1"/>
-    <col min="12" max="12" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.15234375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.84375" style="1"/>
+    <col min="7" max="7" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.84375" style="1"/>
+    <col min="12" max="12" width="8.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.84375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.84375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="10.83203125" style="1"/>
+    <col min="23" max="16384" width="10.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,63 +630,63 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>50.930999999999997</v>
@@ -763,9 +761,9 @@
         <v>9.1236049671039501E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>51.072800000000001</v>
@@ -840,9 +838,9 @@
         <v>7.0764231118783896E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="6">
         <v>50.875</v>
@@ -917,9 +915,9 @@
         <v>9.8345133775124299E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>50.791400000000003</v>
@@ -994,9 +992,9 @@
         <v>0.115571341293709</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>50.8264</v>
@@ -1071,9 +1069,9 @@
         <v>8.5301934170288293E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>50.94</v>
@@ -1148,9 +1146,9 @@
         <v>0.113510058120101</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <v>50.7044</v>
@@ -1225,9 +1223,9 @@
         <v>7.3954901924601302E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1">
         <v>50.6372</v>
@@ -1302,9 +1300,9 @@
         <v>4.2576311306481603E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>50.611400000000003</v>
@@ -1379,9 +1377,9 @@
         <v>7.0403248964181403E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1">
         <v>50.647500000000001</v>
@@ -1456,9 +1454,9 @@
         <v>7.1399903929356204E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1">
         <v>50.745600000000003</v>
@@ -1533,9 +1531,9 @@
         <v>6.3354009027024094E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>50.744399999999999</v>
@@ -1610,9 +1608,9 @@
         <v>7.1047112658351702E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1">
         <v>50.558100000000003</v>
@@ -1687,9 +1685,9 @@
         <v>9.1864886215237002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>50.598599999999998</v>
@@ -1764,9 +1762,9 @@
         <v>9.4636730624384602E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1">
         <v>50.573599999999999</v>
@@ -1844,9 +1842,9 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1">
         <v>50.575299999999999</v>
@@ -1921,9 +1919,9 @@
         <v>7.9046173693500393E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>50.577199999999998</v>
@@ -1998,9 +1996,9 @@
         <v>0.166778636314211</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1">
         <v>50.660800000000002</v>
@@ -2075,9 +2073,9 @@
         <v>6.60656677564187E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1">
         <v>50.660299999999999</v>
@@ -2152,9 +2150,9 @@
         <v>9.9112595583038005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>50.878900000000002</v>
@@ -2229,9 +2227,9 @@
         <v>8.43190787659195E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1">
         <v>50.4925</v>
@@ -2306,9 +2304,9 @@
         <v>0.102829166098706</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6">
         <v>50.547199999999997</v>
@@ -2383,9 +2381,9 @@
         <v>0.19620051328833099</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1">
         <v>50.619199999999999</v>
@@ -2460,9 +2458,9 @@
         <v>8.4663213481138394E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1">
         <v>50.401400000000002</v>
@@ -2537,9 +2535,9 @@
         <v>8.5229776112861297E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1">
         <v>50.441400000000002</v>
@@ -2614,9 +2612,9 @@
         <v>8.1574358055355498E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1">
         <v>50.447499999999998</v>
@@ -2691,9 +2689,9 @@
         <v>9.0020667962120396E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1">
         <v>50.447499999999998</v>
@@ -2768,9 +2766,9 @@
         <v>0.142809433350256</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1">
         <v>50.4756</v>
@@ -2845,7 +2843,7 @@
         <v>9.9448984925731898E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
@@ -2860,5 +2858,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>